--- a/data.mn/public/datasets/temperature-regional.xlsx
+++ b/data.mn/public/datasets/temperature-regional.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1290"/>
+  <dimension ref="A1:C1295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -19773,6 +19773,81 @@
         <v>13</v>
       </c>
     </row>
+    <row r="1291">
+      <c r="A1291" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B1291" t="inlineStr">
+        <is>
+          <t>Choibalsan</t>
+        </is>
+      </c>
+      <c r="C1291" t="n">
+        <v>22.4</v>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B1292" t="inlineStr">
+        <is>
+          <t>Dalanzadgad</t>
+        </is>
+      </c>
+      <c r="C1292" t="n">
+        <v>24.6</v>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B1293" t="inlineStr">
+        <is>
+          <t>Darkhan</t>
+        </is>
+      </c>
+      <c r="C1293" t="n">
+        <v>21.3</v>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B1294" t="inlineStr">
+        <is>
+          <t>Khovd</t>
+        </is>
+      </c>
+      <c r="C1294" t="n">
+        <v>22.4</v>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B1295" t="inlineStr">
+        <is>
+          <t>Ulaanbaatar</t>
+        </is>
+      </c>
+      <c r="C1295" t="n">
+        <v>19.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
